--- a/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2015/TENNESSEE_2015.xlsx
+++ b/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2015/TENNESSEE_2015.xlsx
@@ -3732,7 +3732,7 @@
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>General Simon Bolivar</t>
+          <t>Gral. Simon Bolivar</t>
         </is>
       </c>
       <c r="C188">
@@ -3757,7 +3757,7 @@
         <v>16</v>
       </c>
       <c r="D189">
-        <v>0.0009887529353602769</v>
+        <v>0.0009887529353602767</v>
       </c>
     </row>
     <row r="190">
@@ -6162,7 +6162,7 @@
       </c>
       <c r="B323" t="inlineStr">
         <is>
-          <t>Dolores Hidalgo Cuna De La Independencia Nacional</t>
+          <t>Dolores Hidalgo</t>
         </is>
       </c>
       <c r="C323">
@@ -6619,7 +6619,7 @@
         <v>16</v>
       </c>
       <c r="D348">
-        <v>0.0009887529353602769</v>
+        <v>0.0009887529353602767</v>
       </c>
     </row>
     <row r="349">
@@ -6691,7 +6691,7 @@
         <v>16</v>
       </c>
       <c r="D352">
-        <v>0.0009887529353602769</v>
+        <v>0.0009887529353602767</v>
       </c>
     </row>
     <row r="353">
@@ -6781,7 +6781,7 @@
         <v>157</v>
       </c>
       <c r="D357">
-        <v>0.009702138178222717</v>
+        <v>0.009702138178222715</v>
       </c>
     </row>
     <row r="358">
@@ -7681,7 +7681,7 @@
         <v>16</v>
       </c>
       <c r="D407">
-        <v>0.0009887529353602769</v>
+        <v>0.0009887529353602767</v>
       </c>
     </row>
     <row r="408">
@@ -7771,7 +7771,7 @@
         <v>16</v>
       </c>
       <c r="D412">
-        <v>0.0009887529353602769</v>
+        <v>0.0009887529353602767</v>
       </c>
     </row>
     <row r="413">
@@ -9985,7 +9985,7 @@
         <v>16</v>
       </c>
       <c r="D535">
-        <v>0.0009887529353602769</v>
+        <v>0.0009887529353602767</v>
       </c>
     </row>
     <row r="536">
@@ -13153,7 +13153,7 @@
         <v>16</v>
       </c>
       <c r="D711">
-        <v>0.0009887529353602769</v>
+        <v>0.0009887529353602767</v>
       </c>
     </row>
     <row r="712">
@@ -13344,7 +13344,7 @@
       </c>
       <c r="B722" t="inlineStr">
         <is>
-          <t>General Escobedo</t>
+          <t>Gral. Escobedo</t>
         </is>
       </c>
       <c r="C722">
@@ -13380,7 +13380,7 @@
       </c>
       <c r="B724" t="inlineStr">
         <is>
-          <t>General Zaragoza</t>
+          <t>Gral. Zaragoza</t>
         </is>
       </c>
       <c r="C724">
@@ -15180,7 +15180,7 @@
       </c>
       <c r="B824" t="inlineStr">
         <is>
-          <t>San Juan Mixtepec - Distr. 08 -</t>
+          <t>San Juan Mixtepec -Dto. 08 -</t>
         </is>
       </c>
       <c r="C824">
@@ -15198,7 +15198,7 @@
       </c>
       <c r="B825" t="inlineStr">
         <is>
-          <t>San Juan Mixtepec - Distr. 26 -</t>
+          <t>San Juan Mixtepec -Dto. 26 -</t>
         </is>
       </c>
       <c r="C825">
@@ -15882,7 +15882,7 @@
       </c>
       <c r="B863" t="inlineStr">
         <is>
-          <t>San Pedro Mixtepec - Distr. 22 -</t>
+          <t>San Pedro Mixtepec -Dto. 22 -</t>
         </is>
       </c>
       <c r="C863">
@@ -15900,7 +15900,7 @@
       </c>
       <c r="B864" t="inlineStr">
         <is>
-          <t>San Pedro Mixtepec - Distr. 26 -</t>
+          <t>San Pedro Mixtepec -Dto. 26 -</t>
         </is>
       </c>
       <c r="C864">
@@ -22099,7 +22099,7 @@
         <v>16</v>
       </c>
       <c r="D1208">
-        <v>0.0009887529353602769</v>
+        <v>0.0009887529353602767</v>
       </c>
     </row>
     <row r="1209">
@@ -22866,7 +22866,7 @@
       </c>
       <c r="B1251" t="inlineStr">
         <is>
-          <t>Ziltlaltepec De Trinidad Sanchez Santos</t>
+          <t>Zitlaltepec De Trinidad Sanchez Santos</t>
         </is>
       </c>
       <c r="C1251">
@@ -24439,7 +24439,7 @@
         <v>16</v>
       </c>
       <c r="D1338">
-        <v>0.0009887529353602769</v>
+        <v>0.0009887529353602767</v>
       </c>
     </row>
     <row r="1339">
@@ -24853,7 +24853,7 @@
         <v>16</v>
       </c>
       <c r="D1361">
-        <v>0.0009887529353602769</v>
+        <v>0.0009887529353602767</v>
       </c>
     </row>
     <row r="1362">
@@ -26149,7 +26149,7 @@
         <v>16</v>
       </c>
       <c r="D1433">
-        <v>0.0009887529353602769</v>
+        <v>0.0009887529353602767</v>
       </c>
     </row>
     <row r="1434">
